--- a/docs/AD210/AD210_UT_정기점검계획_양식.xlsx
+++ b/docs/AD210/AD210_UT_정기점검계획_양식.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="57975" yWindow="0" windowWidth="24960" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="57975" yWindow="2925" windowWidth="24960" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="테스트 케이스" sheetId="1" state="visible" r:id="rId1"/>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>① 공장명 + 담당자  ② 예방작업번호 + 설비 를 함께 입력 후 검색</t>
+          <t>① 작업명 + 예방작업번호  ② 예방작업번호 + 설비 를 함께 입력 후 검색</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>이 테스트에서 만든 작업계획 행을 체크 → 삭제 → OK (탭별로 확인)</t>
+          <t>이 테스트에서 만든 작업계획 행을 체크 → 삭제 → OK (카렌다(연간), 목록(조건) 탭에서 각각)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2379,18 +2379,17 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Setting 팝업이 열리는지 확인한다.</t>
+          <t>Setting(Field 설정, Tab 설정) 변경이 화면에 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>검색, 목록, 상세 영역의 Setting 버튼을 각각 클릭</t>
+          <t>검색·목록 영역의 Setting 클릭 → Field 설정에서 한 항목의 화면표시명 변경, Display 여부 N, 정렬값 변경 → 저장 / Tab 설정에서 하위 탭 하나의 Display 여부 N → 저장 → 화면 다시 열어 확인 → [초기화] → 화면 확인 → 원래 값으로 되돌림</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>각 영역의 Setting(Field 설정) 팝업이 열림
-※ Setting 상세 동작(정렬값, Display, 화면표시명, 너비 등)은 공통 기능 문서에서 한 번만 확인</t>
+          <t>Setting 팝업이 열리고, 바꾼 화면표시명이 라벨·헤더·탭 이름에 보이며, Display N 항목은 숨겨지고, 정렬값대로 순서가 바뀜. [초기화] 하면 바로(다시 로그인하지 않아도) 기본 화면으로 돌아옴. 되돌린 뒤에는 원래 화면과 같음 (Setting 은 사용자별 저장)</t>
         </is>
       </c>
       <c r="H32" s="10">
@@ -2732,7 +2731,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>"확정된건이 있습니다. 데이타를 확인하세요." 팝업, 상태가 바뀌지 않음</t>
+          <t>"계획중인 건만 확정 가능합니다." 팝업, 상태가 바뀌지 않음</t>
         </is>
       </c>
       <c r="H38" s="10">
@@ -2785,17 +2784,17 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>목록에서 일정조정 날짜를 바로 수정한다.</t>
+          <t>목록에서 비고를 바로 수정한다. (Edit)</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Edit 클릭 → 작업계획 행의 일정조정(작업일자) 칸을 다른 날짜로 수정 → 저장 → OK</t>
+          <t>Edit 클릭 → 작업계획 행의 비고 칸 클릭 후 수정 → 저장 → OK</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>수정 모드로 바뀌어 저장/취소 버튼이 보이고, 저장 후 목록과 상세의 작업일자가 바뀐 날짜로 표시됨</t>
+          <t>수정 모드 안내와 함께 저장/취소 버튼이 보이고, 저장 후 다시 검색하면 바뀐 비고가 표시됨 (Edit 로 수정할 수 있는 칸은 비고)</t>
         </is>
       </c>
       <c r="H39" s="10">
@@ -2840,17 +2839,17 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>목록 수정을 취소한다.</t>
+          <t>목록 수정을 취소한다. (Edit)</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Edit 클릭 → 일정조정 칸 수정 → 취소</t>
+          <t>Edit 클릭 → 비고 칸 수정 → 취소</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>수정 모드가 끝나고 목록 값이 수정 전으로 돌아감 (새로고침하지 않아도)</t>
+          <t>수정 취소 안내 후 수정 모드가 끝나고 목록 값이 수정 전으로 돌아감 (새로고침하지 않아도)</t>
         </is>
       </c>
       <c r="H40" s="10">
@@ -3913,12 +3912,12 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Edit로 작업발행·작업완료 건의 날짜를 바꾼다.</t>
+          <t>Edit로 작업발행·작업완료 건을 수정한다.</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Edit → 작업발행, 작업완료 행의 일정조정 칸 수정 → 저장</t>
+          <t>Edit → 작업발행, 작업완료 행의 비고 칸 수정 → 저장</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">

--- a/docs/AD210/AD210_UT_정기점검계획_양식.xlsx
+++ b/docs/AD210/AD210_UT_정기점검계획_양식.xlsx
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>체크 없이 일정확정하기 → OK</t>
+          <t>목록을 조회한 뒤 체크 없이 일정확정하기</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>일정추가 계획일자에 어제 날짜 입력 → 저장</t>
+          <t>일정추가 → 계획일자 칸 클릭 → 달력에서 어제 날짜 선택 → 저장</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>형식이 틀린 값은 막히고, 지난 날짜는 안내 후 저장되지 않음</t>
+          <t>형식이 틀린 값은 막히고, 지난 날짜로 바꾸는 것은 허용됨 (사양 확인 2026-10-21)</t>
         </is>
       </c>
       <c r="H62" s="10">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>입력이 막히거나 안내 팝업, 저장되지 않음</t>
+          <t>종료가 시작보다 앞이면 종료일자가 지워져 그대로 저장되지 않음 (사양 확인 2026-10-21)</t>
         </is>
       </c>
       <c r="H64" s="10">

--- a/docs/AD210/AD210_UT_정기점검계획_양식.xlsx
+++ b/docs/AD210/AD210_UT_정기점검계획_양식.xlsx
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>"오늘 및 최종작업 완료일 이후로 생성" 안내 후 저장되지 않음</t>
+          <t>지난 날짜도 계획이 생성됨 (사양 확인 2026-10-21: 팝업 안내는 권고, 생성 허용)</t>
         </is>
       </c>
       <c r="H58" s="10">
